--- a/B/chrVIII:46887-140660_51_finemapping.xlsx
+++ b/B/chrVIII:46887-140660_51_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3719" uniqueCount="3719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3711" uniqueCount="3711">
   <si>
     <t xml:space="preserve">seqnames</t>
   </si>
@@ -10028,19 +10028,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -10476,21 +10467,6 @@
   </si>
   <si>
     <t xml:space="preserve">DDR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -11833,48 +11809,42 @@
         <v>3334</v>
       </c>
       <c r="Z1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3335</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3336</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3337</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3338</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3339</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3340</v>
       </c>
-      <c r="AF1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3341</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3342</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3343</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>3346</v>
+        <v>3343</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -11928,62 +11898,60 @@
         <v>119938</v>
       </c>
       <c r="U2" t="s">
-        <v>3347</v>
+        <v>3344</v>
       </c>
       <c r="V2" t="n">
         <v>436471</v>
       </c>
       <c r="W2" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.369206665388357</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0349959678127997</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3347</v>
       </c>
       <c r="AD2" t="s">
         <v>38</v>
       </c>
       <c r="AE2" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>3347</v>
+      </c>
+      <c r="AF2" t="n">
         <v>4</v>
       </c>
-      <c r="AI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>3351</v>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>3348</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>3352</v>
+        <v>3349</v>
       </c>
       <c r="D3" t="s">
-        <v>3353</v>
+        <v>3350</v>
       </c>
       <c r="E3" t="n">
         <v>115855</v>
@@ -12034,62 +12002,60 @@
         <v>120247</v>
       </c>
       <c r="U3" t="s">
-        <v>3354</v>
+        <v>3351</v>
       </c>
       <c r="V3" t="n">
         <v>703699</v>
       </c>
       <c r="W3" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.380547845973494</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0539875724547854</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3352</v>
       </c>
       <c r="AD3" t="s">
         <v>38</v>
       </c>
       <c r="AE3" t="s">
-        <v>3355</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3355</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>3352</v>
+      </c>
+      <c r="AF3" t="n">
         <v>3</v>
       </c>
-      <c r="AI3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>3356</v>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>3353</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>3357</v>
+        <v>3354</v>
       </c>
       <c r="D4" t="s">
-        <v>3358</v>
+        <v>3355</v>
       </c>
       <c r="E4" t="n">
         <v>48147</v>
@@ -12140,59 +12106,57 @@
         <v>53107</v>
       </c>
       <c r="U4" t="s">
-        <v>3359</v>
+        <v>3356</v>
       </c>
       <c r="V4" t="n">
         <v>35383</v>
       </c>
       <c r="W4" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.69746418727948</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.103538043687651</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3359</v>
       </c>
       <c r="AD4" t="s">
         <v>38</v>
       </c>
       <c r="AE4" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>3359</v>
+      </c>
+      <c r="AF4" t="n">
         <v>4</v>
       </c>
-      <c r="AI4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>3357</v>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>3354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>3363</v>
+        <v>3360</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -12246,62 +12210,60 @@
         <v>115855</v>
       </c>
       <c r="U5" t="s">
-        <v>3364</v>
+        <v>3361</v>
       </c>
       <c r="V5" t="n">
         <v>205635</v>
       </c>
       <c r="W5" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.715954936601028</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.106609103836701</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3362</v>
       </c>
       <c r="AD5" t="s">
         <v>38</v>
       </c>
       <c r="AE5" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>3362</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="b">
+      <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>3363</v>
+      <c r="AH5" t="s">
+        <v>3360</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>3366</v>
+        <v>3363</v>
       </c>
       <c r="D6" t="s">
-        <v>3367</v>
+        <v>3364</v>
       </c>
       <c r="E6" t="n">
         <v>48147</v>
@@ -12352,62 +12314,60 @@
         <v>48147</v>
       </c>
       <c r="U6" t="s">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="V6" t="n">
         <v>371959</v>
       </c>
       <c r="W6" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.47149783940928</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.075439852910182</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3366</v>
       </c>
       <c r="AD6" t="s">
         <v>38</v>
       </c>
       <c r="AE6" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>3370</v>
+        <v>3366</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>3367</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>3371</v>
+        <v>3368</v>
       </c>
       <c r="D7" t="s">
-        <v>3358</v>
+        <v>3355</v>
       </c>
       <c r="E7" t="n">
         <v>48147</v>
@@ -12458,59 +12418,57 @@
         <v>53107</v>
       </c>
       <c r="U7" t="s">
-        <v>3372</v>
+        <v>3369</v>
       </c>
       <c r="V7" t="n">
         <v>1074213</v>
       </c>
       <c r="W7" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.448651032049478</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0767155837755129</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3370</v>
       </c>
       <c r="AD7" t="s">
         <v>38</v>
       </c>
       <c r="AE7" t="s">
-        <v>3373</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3373</v>
-      </c>
-      <c r="AH7" t="n">
+        <v>3370</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" t="b">
+      <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>3371</v>
+      <c r="AH7" t="s">
+        <v>3368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>3374</v>
+        <v>3371</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -12564,62 +12522,60 @@
         <v>115855</v>
       </c>
       <c r="U8" t="s">
-        <v>3364</v>
+        <v>3361</v>
       </c>
       <c r="V8" t="n">
         <v>322342</v>
       </c>
       <c r="W8" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.26462927674255</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0463702778777913</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3362</v>
       </c>
       <c r="AD8" t="s">
         <v>38</v>
       </c>
       <c r="AE8" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>3375</v>
+        <v>3362</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>3372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>3376</v>
+        <v>3373</v>
       </c>
       <c r="D9" t="s">
-        <v>3377</v>
+        <v>3374</v>
       </c>
       <c r="E9" t="n">
         <v>95107</v>
@@ -12670,59 +12626,57 @@
         <v>108134</v>
       </c>
       <c r="U9" t="s">
-        <v>3378</v>
+        <v>3375</v>
       </c>
       <c r="V9" t="n">
         <v>267314</v>
       </c>
       <c r="W9" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.422241334974382</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.105663474538131</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3376</v>
       </c>
       <c r="AD9" t="s">
         <v>38</v>
       </c>
       <c r="AE9" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AH9" t="n">
+        <v>3376</v>
+      </c>
+      <c r="AF9" t="n">
         <v>4</v>
       </c>
-      <c r="AI9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>3380</v>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>3377</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>3381</v>
+        <v>3378</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -12776,59 +12730,57 @@
         <v>121609</v>
       </c>
       <c r="U10" t="s">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="V10" t="n">
         <v>316968</v>
       </c>
       <c r="W10" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-0.632688945978726</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.151230654588718</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3366</v>
       </c>
       <c r="AD10" t="s">
         <v>38</v>
       </c>
       <c r="AE10" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>3366</v>
+      </c>
+      <c r="AF10" t="n">
         <v>3</v>
       </c>
-      <c r="AI10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>3382</v>
+      <c r="AG10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>3379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>3383</v>
+        <v>3380</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
@@ -12882,59 +12834,57 @@
         <v>115855</v>
       </c>
       <c r="U11" t="s">
-        <v>3384</v>
+        <v>3381</v>
       </c>
       <c r="V11" t="n">
         <v>1385176</v>
       </c>
       <c r="W11" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.116158425257123</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0253936893139469</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3382</v>
       </c>
       <c r="AD11" t="s">
         <v>38</v>
       </c>
       <c r="AE11" t="s">
-        <v>3385</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3385</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>3382</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" t="b">
+      <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>3386</v>
+      <c r="AH11" t="s">
+        <v>3383</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>3387</v>
+        <v>3384</v>
       </c>
       <c r="D12" t="s">
         <v>111</v>
@@ -12988,59 +12938,57 @@
         <v>121030</v>
       </c>
       <c r="U12" t="s">
-        <v>3347</v>
+        <v>3344</v>
       </c>
       <c r="V12" t="n">
         <v>344671</v>
       </c>
       <c r="W12" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.158517961781725</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0394392096563056</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3347</v>
       </c>
       <c r="AD12" t="s">
         <v>38</v>
       </c>
       <c r="AE12" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AH12" t="n">
+        <v>3347</v>
+      </c>
+      <c r="AF12" t="n">
         <v>3</v>
       </c>
-      <c r="AI12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>3388</v>
+      <c r="AG12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>3385</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>3389</v>
+        <v>3386</v>
       </c>
       <c r="D13" t="s">
         <v>37</v>
@@ -13094,62 +13042,60 @@
         <v>119938</v>
       </c>
       <c r="U13" t="s">
-        <v>3390</v>
+        <v>3387</v>
       </c>
       <c r="V13" t="n">
         <v>82580</v>
       </c>
       <c r="W13" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.119890574665399</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0262392510601575</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3388</v>
       </c>
       <c r="AD13" t="s">
         <v>38</v>
       </c>
       <c r="AE13" t="s">
-        <v>3391</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3391</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>3388</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" t="b">
+      <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>3392</v>
+      <c r="AH13" t="s">
+        <v>3389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>3393</v>
+        <v>3390</v>
       </c>
       <c r="D14" t="s">
-        <v>3377</v>
+        <v>3374</v>
       </c>
       <c r="E14" t="n">
         <v>103046</v>
@@ -13200,59 +13146,57 @@
         <v>108134</v>
       </c>
       <c r="U14" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V14" t="n">
         <v>179897</v>
       </c>
       <c r="W14" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.540447732139791</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.141730624349188</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3392</v>
       </c>
       <c r="AD14" t="s">
         <v>38</v>
       </c>
       <c r="AE14" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH14" t="n">
+        <v>3392</v>
+      </c>
+      <c r="AF14" t="n">
         <v>3</v>
       </c>
-      <c r="AI14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>3396</v>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>3393</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>3397</v>
+        <v>3394</v>
       </c>
       <c r="D15" t="s">
         <v>37</v>
@@ -13306,62 +13250,60 @@
         <v>119938</v>
       </c>
       <c r="U15" t="s">
-        <v>3364</v>
+        <v>3361</v>
       </c>
       <c r="V15" t="n">
         <v>282909</v>
       </c>
       <c r="W15" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-0.606761222624135</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.175326763222877</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3362</v>
       </c>
       <c r="AD15" t="s">
         <v>38</v>
       </c>
       <c r="AE15" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>3362</v>
+      </c>
+      <c r="AF15" t="n">
         <v>3</v>
       </c>
-      <c r="AI15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>3398</v>
+      <c r="AG15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>3395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>3399</v>
+        <v>3396</v>
       </c>
       <c r="D16" t="s">
-        <v>3400</v>
+        <v>3397</v>
       </c>
       <c r="E16" t="n">
         <v>103046</v>
@@ -13412,62 +13354,60 @@
         <v>107309</v>
       </c>
       <c r="U16" t="s">
-        <v>3364</v>
+        <v>3361</v>
       </c>
       <c r="V16" t="n">
         <v>140493</v>
       </c>
       <c r="W16" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.328869560426771</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0861483110985055</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3362</v>
       </c>
       <c r="AD16" t="s">
         <v>38</v>
       </c>
       <c r="AE16" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3365</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>3401</v>
+        <v>3362</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>3398</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>3402</v>
+        <v>3399</v>
       </c>
       <c r="D17" t="s">
-        <v>3400</v>
+        <v>3397</v>
       </c>
       <c r="E17" t="n">
         <v>95107</v>
@@ -13518,62 +13458,60 @@
         <v>107309</v>
       </c>
       <c r="U17" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V17" t="n">
         <v>399702</v>
       </c>
       <c r="W17" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.337631606909368</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.100049062133157</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3392</v>
       </c>
       <c r="AD17" t="s">
         <v>38</v>
       </c>
       <c r="AE17" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>3392</v>
+      </c>
+      <c r="AF17" t="n">
         <v>3</v>
       </c>
-      <c r="AI17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>3403</v>
+      <c r="AG17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>3400</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>3404</v>
+        <v>3401</v>
       </c>
       <c r="D18" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="E18" t="n">
         <v>53107</v>
@@ -13624,59 +13562,57 @@
         <v>67971</v>
       </c>
       <c r="U18" t="s">
-        <v>3406</v>
+        <v>3403</v>
       </c>
       <c r="V18" t="n">
         <v>261132</v>
       </c>
       <c r="W18" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.200382692158732</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0584537558650337</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3404</v>
       </c>
       <c r="AD18" t="s">
         <v>38</v>
       </c>
       <c r="AE18" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>3404</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" t="b">
+      <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>3408</v>
+      <c r="AH18" t="s">
+        <v>3405</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>3409</v>
+        <v>3406</v>
       </c>
       <c r="D19" t="s">
         <v>37</v>
@@ -13730,62 +13666,60 @@
         <v>119938</v>
       </c>
       <c r="U19" t="s">
-        <v>3354</v>
+        <v>3351</v>
       </c>
       <c r="V19" t="n">
         <v>110917</v>
       </c>
       <c r="W19" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.452626814622415</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.116420052142419</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>3352</v>
       </c>
       <c r="AD19" t="s">
         <v>38</v>
       </c>
       <c r="AE19" t="s">
-        <v>3355</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>3355</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>3352</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="b">
+      <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>3410</v>
+      <c r="AH19" t="s">
+        <v>3407</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>3411</v>
+        <v>3408</v>
       </c>
       <c r="D20" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="E20" t="n">
         <v>67971</v>
@@ -13836,62 +13770,60 @@
         <v>67971</v>
       </c>
       <c r="U20" t="s">
-        <v>3390</v>
+        <v>3387</v>
       </c>
       <c r="V20" t="n">
         <v>107256</v>
       </c>
       <c r="W20" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.104837820352317</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0275342339379878</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3388</v>
       </c>
       <c r="AD20" t="s">
         <v>38</v>
       </c>
       <c r="AE20" t="s">
-        <v>3391</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3391</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>3388</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>3412</v>
+      <c r="AH20" t="s">
+        <v>3409</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>3413</v>
+        <v>3410</v>
       </c>
       <c r="D21" t="s">
-        <v>3358</v>
+        <v>3355</v>
       </c>
       <c r="E21" t="n">
         <v>48147</v>
@@ -13942,62 +13874,60 @@
         <v>53107</v>
       </c>
       <c r="U21" t="s">
-        <v>3378</v>
+        <v>3375</v>
       </c>
       <c r="V21" t="n">
         <v>73285</v>
       </c>
       <c r="W21" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.110980748924662</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0372551268681647</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3376</v>
       </c>
       <c r="AD21" t="s">
         <v>38</v>
       </c>
       <c r="AE21" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>3414</v>
+        <v>3376</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>3411</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>3415</v>
+        <v>3412</v>
       </c>
       <c r="D22" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="E22" t="n">
         <v>53107</v>
@@ -14048,62 +13978,60 @@
         <v>67971</v>
       </c>
       <c r="U22" t="s">
-        <v>3416</v>
+        <v>3413</v>
       </c>
       <c r="V22" t="n">
         <v>130799</v>
       </c>
       <c r="W22" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.0831623256631903</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0244492670322812</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3414</v>
       </c>
       <c r="AD22" t="s">
         <v>38</v>
       </c>
       <c r="AE22" t="s">
-        <v>3417</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3417</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>3414</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" t="b">
+      <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>3418</v>
+      <c r="AH22" t="s">
+        <v>3415</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>3419</v>
+        <v>3416</v>
       </c>
       <c r="D23" t="s">
-        <v>3358</v>
+        <v>3355</v>
       </c>
       <c r="E23" t="n">
         <v>48147</v>
@@ -14154,59 +14082,57 @@
         <v>53107</v>
       </c>
       <c r="U23" t="s">
-        <v>3420</v>
+        <v>3417</v>
       </c>
       <c r="V23" t="n">
         <v>14933</v>
       </c>
       <c r="W23" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.490393444259338</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.142279077621352</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3418</v>
       </c>
       <c r="AD23" t="s">
         <v>38</v>
       </c>
       <c r="AE23" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>3418</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>3419</v>
+      <c r="AH23" t="s">
+        <v>3416</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>3422</v>
+        <v>3419</v>
       </c>
       <c r="D24" t="s">
         <v>37</v>
@@ -14260,59 +14186,57 @@
         <v>119938</v>
       </c>
       <c r="U24" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V24" t="n">
         <v>736926</v>
       </c>
       <c r="W24" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-0.275536057388593</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.093695998693257</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>3392</v>
       </c>
       <c r="AD24" t="s">
         <v>38</v>
       </c>
       <c r="AE24" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>3423</v>
+        <v>3392</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>3420</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>3424</v>
+        <v>3421</v>
       </c>
       <c r="D25" t="s">
         <v>111</v>
@@ -14366,62 +14290,60 @@
         <v>121030</v>
       </c>
       <c r="U25" t="s">
-        <v>3378</v>
+        <v>3375</v>
       </c>
       <c r="V25" t="n">
         <v>71683</v>
       </c>
       <c r="W25" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-0.27341945162835</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0873752886770477</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>3376</v>
       </c>
       <c r="AD25" t="s">
         <v>38</v>
       </c>
       <c r="AE25" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AH25" t="n">
+        <v>3376</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" t="b">
+      <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="s">
-        <v>3425</v>
+      <c r="AH25" t="s">
+        <v>3422</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>3426</v>
+        <v>3423</v>
       </c>
       <c r="D26" t="s">
-        <v>3427</v>
+        <v>3424</v>
       </c>
       <c r="E26" t="n">
         <v>115855</v>
@@ -14472,62 +14394,60 @@
         <v>123980</v>
       </c>
       <c r="U26" t="s">
-        <v>3359</v>
+        <v>3356</v>
       </c>
       <c r="V26" t="n">
         <v>228771</v>
       </c>
       <c r="W26" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.318286378561939</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.118933892681999</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>3359</v>
       </c>
       <c r="AD26" t="s">
         <v>38</v>
       </c>
       <c r="AE26" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>3428</v>
+        <v>3359</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>3425</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>3429</v>
+        <v>3426</v>
       </c>
       <c r="D27" t="s">
-        <v>3353</v>
+        <v>3350</v>
       </c>
       <c r="E27" t="n">
         <v>76139</v>
@@ -14578,62 +14498,60 @@
         <v>120247</v>
       </c>
       <c r="U27" t="s">
-        <v>3347</v>
+        <v>3344</v>
       </c>
       <c r="V27" t="n">
         <v>1057455</v>
       </c>
       <c r="W27" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-0.0488700392714786</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.0161076298042186</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>3347</v>
       </c>
       <c r="AD27" t="s">
         <v>38</v>
       </c>
       <c r="AE27" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AH27" t="n">
+        <v>3347</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="b">
+      <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>3430</v>
+      <c r="AH27" t="s">
+        <v>3427</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B28" t="s">
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>3431</v>
+        <v>3428</v>
       </c>
       <c r="D28" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="E28" t="n">
         <v>67971</v>
@@ -14684,62 +14602,60 @@
         <v>67971</v>
       </c>
       <c r="U28" t="s">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="V28" t="n">
         <v>418537</v>
       </c>
       <c r="W28" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.072647471940456</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.0235059794092803</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>3366</v>
       </c>
       <c r="AD28" t="s">
         <v>38</v>
       </c>
       <c r="AE28" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AH28" t="n">
+        <v>3366</v>
+      </c>
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" t="b">
+      <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="s">
-        <v>3431</v>
+      <c r="AH28" t="s">
+        <v>3428</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B29" t="s">
         <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>3432</v>
+        <v>3429</v>
       </c>
       <c r="D29" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="E29" t="n">
         <v>53107</v>
@@ -14790,59 +14706,57 @@
         <v>67971</v>
       </c>
       <c r="U29" t="s">
-        <v>3420</v>
+        <v>3417</v>
       </c>
       <c r="V29" t="n">
         <v>432588</v>
       </c>
       <c r="W29" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z29" t="n">
         <v>-0.0792141205350523</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.0297099216763846</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>3418</v>
       </c>
       <c r="AD29" t="s">
         <v>38</v>
       </c>
       <c r="AE29" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>3433</v>
+        <v>3418</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>3430</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B30" t="s">
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>3434</v>
+        <v>3431</v>
       </c>
       <c r="D30" t="s">
         <v>34</v>
@@ -14896,59 +14810,57 @@
         <v>115855</v>
       </c>
       <c r="U30" t="s">
-        <v>3435</v>
+        <v>3432</v>
       </c>
       <c r="V30" t="n">
         <v>442789</v>
       </c>
       <c r="W30" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.238363755671227</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.0918339974422641</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>3433</v>
       </c>
       <c r="AD30" t="s">
         <v>38</v>
       </c>
       <c r="AE30" t="s">
-        <v>3436</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>3436</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>3437</v>
+        <v>3433</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>3434</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>3438</v>
+        <v>3435</v>
       </c>
       <c r="D31" t="s">
         <v>37</v>
@@ -15002,62 +14914,60 @@
         <v>119938</v>
       </c>
       <c r="U31" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V31" t="n">
         <v>725814</v>
       </c>
       <c r="W31" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z31" t="n">
         <v>-0.109668077827922</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.0375408387570066</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>3392</v>
       </c>
       <c r="AD31" t="s">
         <v>38</v>
       </c>
       <c r="AE31" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH31" t="n">
+        <v>3392</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" t="b">
+      <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>3439</v>
+      <c r="AH31" t="s">
+        <v>3436</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>3440</v>
+        <v>3437</v>
       </c>
       <c r="D32" t="s">
-        <v>3441</v>
+        <v>3438</v>
       </c>
       <c r="E32" t="n">
         <v>108134</v>
@@ -15108,59 +15018,57 @@
         <v>130538</v>
       </c>
       <c r="U32" t="s">
-        <v>3420</v>
+        <v>3417</v>
       </c>
       <c r="V32" t="n">
         <v>921860</v>
       </c>
       <c r="W32" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="Y32" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.179748734674878</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AA32" t="n">
         <v>0.0604220286855095</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>3418</v>
       </c>
       <c r="AD32" t="s">
         <v>38</v>
       </c>
       <c r="AE32" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AH32" t="n">
+        <v>3418</v>
+      </c>
+      <c r="AF32" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" t="b">
+      <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="s">
-        <v>3442</v>
+      <c r="AH32" t="s">
+        <v>3439</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>3443</v>
+        <v>3440</v>
       </c>
       <c r="D33" t="s">
         <v>34</v>
@@ -15214,62 +15122,60 @@
         <v>115855</v>
       </c>
       <c r="U33" t="s">
-        <v>3406</v>
+        <v>3403</v>
       </c>
       <c r="V33" t="n">
         <v>113095</v>
       </c>
       <c r="W33" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.415236620840984</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
         <v>0.148545030542227</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>3404</v>
       </c>
       <c r="AD33" t="s">
         <v>38</v>
       </c>
       <c r="AE33" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AH33" t="n">
+        <v>3404</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" t="b">
+      <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>3444</v>
+      <c r="AH33" t="s">
+        <v>3441</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>3445</v>
+        <v>3442</v>
       </c>
       <c r="D34" t="s">
-        <v>3367</v>
+        <v>3364</v>
       </c>
       <c r="E34" t="n">
         <v>24334</v>
@@ -15320,59 +15226,57 @@
         <v>48147</v>
       </c>
       <c r="U34" t="s">
-        <v>3384</v>
+        <v>3381</v>
       </c>
       <c r="V34" t="n">
         <v>720813</v>
       </c>
       <c r="W34" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
       </c>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="Y34" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.0475842217126945</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AA34" t="n">
         <v>0.0165907713783064</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>3382</v>
       </c>
       <c r="AD34" t="s">
         <v>38</v>
       </c>
       <c r="AE34" t="s">
-        <v>3385</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>3385</v>
-      </c>
-      <c r="AH34" t="n">
+        <v>3382</v>
+      </c>
+      <c r="AF34" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" t="b">
+      <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>3445</v>
+      <c r="AH34" t="s">
+        <v>3442</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>3446</v>
+        <v>3443</v>
       </c>
       <c r="D35" t="s">
         <v>37</v>
@@ -15426,59 +15330,57 @@
         <v>119938</v>
       </c>
       <c r="U35" t="s">
-        <v>3378</v>
+        <v>3375</v>
       </c>
       <c r="V35" t="n">
         <v>162479</v>
       </c>
       <c r="W35" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
       </c>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="Y35" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z35" t="n">
         <v>-0.0587885144801714</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AA35" t="n">
         <v>0.0196074451247755</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>3376</v>
       </c>
       <c r="AD35" t="s">
         <v>38</v>
       </c>
       <c r="AE35" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>3379</v>
-      </c>
-      <c r="AH35" t="n">
+        <v>3376</v>
+      </c>
+      <c r="AF35" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" t="b">
+      <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>3446</v>
+      <c r="AH35" t="s">
+        <v>3443</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B36" t="s">
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>3447</v>
+        <v>3444</v>
       </c>
       <c r="D36" t="s">
         <v>37</v>
@@ -15532,62 +15434,60 @@
         <v>119938</v>
       </c>
       <c r="U36" t="s">
-        <v>3420</v>
+        <v>3417</v>
       </c>
       <c r="V36" t="n">
         <v>829918</v>
       </c>
       <c r="W36" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
       </c>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="Y36" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.0668516659971748</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AA36" t="n">
         <v>0.0245113887519202</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>3418</v>
       </c>
       <c r="AD36" t="s">
         <v>38</v>
       </c>
       <c r="AE36" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AH36" t="n">
+        <v>3418</v>
+      </c>
+      <c r="AF36" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" t="b">
+      <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="s">
-        <v>3448</v>
+      <c r="AH36" t="s">
+        <v>3445</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>3449</v>
+        <v>3446</v>
       </c>
       <c r="D37" t="s">
-        <v>3367</v>
+        <v>3364</v>
       </c>
       <c r="E37" t="n">
         <v>35854</v>
@@ -15638,62 +15538,60 @@
         <v>48147</v>
       </c>
       <c r="U37" t="s">
-        <v>3420</v>
+        <v>3417</v>
       </c>
       <c r="V37" t="n">
         <v>645950</v>
       </c>
       <c r="W37" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
       </c>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="Y37" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z37" t="n">
         <v>-0.0434563089765998</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AA37" t="n">
         <v>0.0177162034428645</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>3418</v>
       </c>
       <c r="AD37" t="s">
         <v>38</v>
       </c>
       <c r="AE37" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>3450</v>
+        <v>3418</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>3447</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B38" t="s">
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>3451</v>
+        <v>3448</v>
       </c>
       <c r="D38" t="s">
-        <v>3377</v>
+        <v>3374</v>
       </c>
       <c r="E38" t="n">
         <v>103046</v>
@@ -15744,62 +15642,60 @@
         <v>108134</v>
       </c>
       <c r="U38" t="s">
-        <v>3420</v>
+        <v>3417</v>
       </c>
       <c r="V38" t="n">
         <v>700594</v>
       </c>
       <c r="W38" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AA38" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="Y38" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z38" t="n">
         <v>-0.0260902209764916</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AA38" t="n">
         <v>0.0100687087405578</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>3418</v>
       </c>
       <c r="AD38" t="s">
         <v>38</v>
       </c>
       <c r="AE38" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>3421</v>
-      </c>
-      <c r="AH38" t="n">
+        <v>3418</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" t="b">
+      <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="s">
-        <v>3452</v>
+      <c r="AH38" t="s">
+        <v>3449</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B39" t="s">
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>3453</v>
+        <v>3450</v>
       </c>
       <c r="D39" t="s">
-        <v>3400</v>
+        <v>3397</v>
       </c>
       <c r="E39" t="n">
         <v>67971</v>
@@ -15850,59 +15746,57 @@
         <v>107309</v>
       </c>
       <c r="U39" t="s">
-        <v>3354</v>
+        <v>3351</v>
       </c>
       <c r="V39" t="n">
         <v>276502</v>
       </c>
       <c r="W39" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AA39" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="Y39" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z39" t="n">
         <v>-0.111594506950586</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AA39" t="n">
         <v>0.0639340759655712</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>3352</v>
       </c>
       <c r="AD39" t="s">
         <v>38</v>
       </c>
       <c r="AE39" t="s">
-        <v>3355</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>3355</v>
-      </c>
-      <c r="AH39" t="n">
+        <v>3352</v>
+      </c>
+      <c r="AF39" t="n">
         <v>2</v>
       </c>
-      <c r="AI39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>3454</v>
+      <c r="AG39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>3451</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B40" t="s">
         <v>19</v>
       </c>
       <c r="C40" t="s">
-        <v>3455</v>
+        <v>3452</v>
       </c>
       <c r="D40" t="s">
         <v>111</v>
@@ -15956,62 +15850,60 @@
         <v>121030</v>
       </c>
       <c r="U40" t="s">
-        <v>3359</v>
+        <v>3356</v>
       </c>
       <c r="V40" t="n">
         <v>368781</v>
       </c>
       <c r="W40" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
       </c>
-      <c r="Y40"/>
-      <c r="Z40"/>
-      <c r="AA40" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="Y40" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.02712052825863</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AA40" t="n">
         <v>0.0104778583468431</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>3359</v>
       </c>
       <c r="AD40" t="s">
         <v>38</v>
       </c>
       <c r="AE40" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AH40" t="n">
+        <v>3359</v>
+      </c>
+      <c r="AF40" t="n">
         <v>0</v>
       </c>
-      <c r="AI40" t="b">
+      <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>3456</v>
+      <c r="AH40" t="s">
+        <v>3453</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>3457</v>
+        <v>3454</v>
       </c>
       <c r="D41" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="E41" t="n">
         <v>53107</v>
@@ -16062,62 +15954,60 @@
         <v>67971</v>
       </c>
       <c r="U41" t="s">
-        <v>3406</v>
+        <v>3403</v>
       </c>
       <c r="V41" t="n">
         <v>309206</v>
       </c>
       <c r="W41" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
       </c>
-      <c r="Y41"/>
-      <c r="Z41"/>
-      <c r="AA41" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="Y41" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.0672493945703688</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AA41" t="n">
         <v>0.0243755745620886</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>3404</v>
       </c>
       <c r="AD41" t="s">
         <v>38</v>
       </c>
       <c r="AE41" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AH41" t="n">
+        <v>3404</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" t="b">
+      <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="s">
-        <v>3457</v>
+      <c r="AH41" t="s">
+        <v>3454</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B42" t="s">
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>3458</v>
+        <v>3455</v>
       </c>
       <c r="D42" t="s">
-        <v>3459</v>
+        <v>3456</v>
       </c>
       <c r="E42" t="n">
         <v>67971</v>
@@ -16168,62 +16058,60 @@
         <v>76139</v>
       </c>
       <c r="U42" t="s">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="V42" t="n">
         <v>192451</v>
       </c>
       <c r="W42" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
       </c>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AA42" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="Y42" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z42" t="n">
         <v>-0.119295421554012</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AA42" t="n">
         <v>0.0564255201939274</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>3366</v>
       </c>
       <c r="AD42" t="s">
         <v>38</v>
       </c>
       <c r="AE42" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AF42" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>3369</v>
-      </c>
-      <c r="AH42" t="n">
+        <v>3366</v>
+      </c>
+      <c r="AF42" t="n">
         <v>2</v>
       </c>
-      <c r="AI42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>3460</v>
+      <c r="AG42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>3457</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>3461</v>
+        <v>3458</v>
       </c>
       <c r="D43" t="s">
-        <v>3358</v>
+        <v>3355</v>
       </c>
       <c r="E43" t="n">
         <v>48147</v>
@@ -16274,62 +16162,60 @@
         <v>53107</v>
       </c>
       <c r="U43" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V43" t="n">
         <v>659745</v>
       </c>
       <c r="W43" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X43" t="b">
         <v>1</v>
       </c>
-      <c r="Y43"/>
-      <c r="Z43"/>
-      <c r="AA43" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="Y43" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z43" t="n">
         <v>-0.286396275827036</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AA43" t="n">
         <v>0.131368171420313</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>3392</v>
       </c>
       <c r="AD43" t="s">
         <v>38</v>
       </c>
       <c r="AE43" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF43" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG43" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ43" t="s">
-        <v>3462</v>
+        <v>3392</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>3459</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>3463</v>
+        <v>3460</v>
       </c>
       <c r="D44" t="s">
-        <v>3459</v>
+        <v>3456</v>
       </c>
       <c r="E44" t="n">
         <v>67971</v>
@@ -16380,59 +16266,57 @@
         <v>76139</v>
       </c>
       <c r="U44" t="s">
-        <v>3372</v>
+        <v>3369</v>
       </c>
       <c r="V44" t="n">
         <v>219211</v>
       </c>
       <c r="W44" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X44" t="b">
         <v>1</v>
       </c>
-      <c r="Y44"/>
-      <c r="Z44"/>
-      <c r="AA44" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB44" t="n">
+      <c r="Y44" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z44" t="n">
         <v>-0.0639454479230752</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AA44" t="n">
         <v>0.0334853716214918</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>3370</v>
       </c>
       <c r="AD44" t="s">
         <v>38</v>
       </c>
       <c r="AE44" t="s">
-        <v>3373</v>
-      </c>
-      <c r="AF44" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>3373</v>
-      </c>
-      <c r="AH44" t="n">
+        <v>3370</v>
+      </c>
+      <c r="AF44" t="n">
         <v>3</v>
       </c>
-      <c r="AI44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="s">
-        <v>3464</v>
+      <c r="AG44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>3461</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B45" t="s">
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>3465</v>
+        <v>3462</v>
       </c>
       <c r="D45" t="s">
         <v>37</v>
@@ -16486,59 +16370,57 @@
         <v>119938</v>
       </c>
       <c r="U45" t="s">
-        <v>3347</v>
+        <v>3344</v>
       </c>
       <c r="V45" t="n">
         <v>672186</v>
       </c>
       <c r="W45" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X45" t="b">
         <v>1</v>
       </c>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB45" t="n">
+      <c r="Y45" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z45" t="n">
         <v>-0.0736667499015007</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AA45" t="n">
         <v>0.0299996837795003</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>3347</v>
       </c>
       <c r="AD45" t="s">
         <v>38</v>
       </c>
       <c r="AE45" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AF45" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ45" t="s">
-        <v>3466</v>
+        <v>3347</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>3463</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B46" t="s">
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>3467</v>
+        <v>3464</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -16592,62 +16474,60 @@
         <v>122634</v>
       </c>
       <c r="U46" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V46" t="n">
         <v>912760</v>
       </c>
       <c r="W46" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
       </c>
-      <c r="Y46"/>
-      <c r="Z46"/>
-      <c r="AA46" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB46" t="n">
+      <c r="Y46" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.358774337668089</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AA46" t="n">
         <v>0.136488536567062</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>3392</v>
       </c>
       <c r="AD46" t="s">
         <v>38</v>
       </c>
       <c r="AE46" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH46" t="n">
+        <v>3392</v>
+      </c>
+      <c r="AF46" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" t="b">
+      <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="s">
-        <v>3468</v>
+      <c r="AH46" t="s">
+        <v>3465</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>3469</v>
+        <v>3466</v>
       </c>
       <c r="D47" t="s">
-        <v>3470</v>
+        <v>3467</v>
       </c>
       <c r="E47" t="n">
         <v>67971</v>
@@ -16698,62 +16578,60 @@
         <v>92343</v>
       </c>
       <c r="U47" t="s">
-        <v>3406</v>
+        <v>3403</v>
       </c>
       <c r="V47" t="n">
         <v>463959</v>
       </c>
       <c r="W47" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X47" t="b">
         <v>1</v>
       </c>
-      <c r="Y47"/>
-      <c r="Z47"/>
-      <c r="AA47" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB47" t="n">
+      <c r="Y47" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z47" t="n">
         <v>-0.106511759570192</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AA47" t="n">
         <v>0.0618529196901417</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>3404</v>
       </c>
       <c r="AD47" t="s">
         <v>38</v>
       </c>
       <c r="AE47" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ47" t="s">
-        <v>3471</v>
+        <v>3404</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>3468</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>3472</v>
+        <v>3469</v>
       </c>
       <c r="D48" t="s">
-        <v>3473</v>
+        <v>3470</v>
       </c>
       <c r="E48" t="n">
         <v>67971</v>
@@ -16804,62 +16682,60 @@
         <v>72104</v>
       </c>
       <c r="U48" t="s">
-        <v>3359</v>
+        <v>3356</v>
       </c>
       <c r="V48" t="n">
         <v>369547</v>
       </c>
       <c r="W48" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="X48" t="b">
         <v>1</v>
       </c>
-      <c r="Y48"/>
-      <c r="Z48"/>
-      <c r="AA48" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AB48" t="n">
+      <c r="Y48" t="s">
+        <v>3358</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.0177774738078019</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AA48" t="n">
         <v>0.00733589659816136</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>3359</v>
       </c>
       <c r="AD48" t="s">
         <v>38</v>
       </c>
       <c r="AE48" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG48" t="s">
-        <v>3362</v>
-      </c>
-      <c r="AH48" t="n">
+        <v>3359</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0</v>
       </c>
-      <c r="AI48" t="b">
+      <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="s">
-        <v>3474</v>
+      <c r="AH48" t="s">
+        <v>3471</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B49" t="s">
         <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>3475</v>
+        <v>3472</v>
       </c>
       <c r="D49" t="s">
-        <v>3377</v>
+        <v>3374</v>
       </c>
       <c r="E49" t="n">
         <v>67971</v>
@@ -16910,59 +16786,57 @@
         <v>108134</v>
       </c>
       <c r="U49" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V49" t="n">
         <v>220138</v>
       </c>
       <c r="W49" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
       </c>
-      <c r="Y49"/>
-      <c r="Z49"/>
-      <c r="AA49" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB49" t="n">
+      <c r="Y49" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.0409393509712187</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AA49" t="n">
         <v>0.0157061949283742</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>3392</v>
       </c>
       <c r="AD49" t="s">
         <v>38</v>
       </c>
       <c r="AE49" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG49" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH49" t="n">
+        <v>3392</v>
+      </c>
+      <c r="AF49" t="n">
         <v>0</v>
       </c>
-      <c r="AI49" t="b">
+      <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="s">
-        <v>3476</v>
+      <c r="AH49" t="s">
+        <v>3473</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B50" t="s">
         <v>19</v>
       </c>
       <c r="C50" t="s">
-        <v>3477</v>
+        <v>3474</v>
       </c>
       <c r="D50" t="s">
         <v>34</v>
@@ -17016,59 +16890,57 @@
         <v>115855</v>
       </c>
       <c r="U50" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V50" t="n">
         <v>181474</v>
       </c>
       <c r="W50" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X50" t="b">
         <v>1</v>
       </c>
-      <c r="Y50"/>
-      <c r="Z50"/>
-      <c r="AA50" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="Y50" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z50" t="n">
         <v>-0.219637175702052</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AA50" t="n">
         <v>0.0972600935368205</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>3392</v>
       </c>
       <c r="AD50" t="s">
         <v>38</v>
       </c>
       <c r="AE50" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG50" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH50" t="n">
+        <v>3392</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" t="b">
+      <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="s">
-        <v>3478</v>
+      <c r="AH50" t="s">
+        <v>3475</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B51" t="s">
         <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>3479</v>
+        <v>3476</v>
       </c>
       <c r="D51" t="s">
         <v>34</v>
@@ -17122,62 +16994,60 @@
         <v>115855</v>
       </c>
       <c r="U51" t="s">
-        <v>3394</v>
+        <v>3391</v>
       </c>
       <c r="V51" t="n">
         <v>878900</v>
       </c>
       <c r="W51" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X51" t="b">
         <v>1</v>
       </c>
-      <c r="Y51"/>
-      <c r="Z51"/>
-      <c r="AA51" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="Y51" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z51" t="n">
         <v>-0.132793497668105</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AA51" t="n">
         <v>0.0781969174436409</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>3392</v>
       </c>
       <c r="AD51" t="s">
         <v>38</v>
       </c>
       <c r="AE51" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AF51" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG51" t="s">
-        <v>3395</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ51" t="s">
-        <v>3480</v>
+        <v>3392</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>3477</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>3345</v>
+        <v>3342</v>
       </c>
       <c r="B52" t="s">
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>3481</v>
+        <v>3478</v>
       </c>
       <c r="D52" t="s">
-        <v>3482</v>
+        <v>3479</v>
       </c>
       <c r="E52" t="n">
         <v>92343</v>
@@ -17228,48 +17098,46 @@
         <v>103046</v>
       </c>
       <c r="U52" t="s">
-        <v>3372</v>
+        <v>3369</v>
       </c>
       <c r="V52" t="n">
         <v>231281</v>
       </c>
       <c r="W52" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="X52" t="b">
         <v>1</v>
       </c>
-      <c r="Y52"/>
-      <c r="Z52"/>
-      <c r="AA52" t="s">
-        <v>3349</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="Y52" t="s">
+        <v>3346</v>
+      </c>
+      <c r="Z52" t="n">
         <v>0.0723306416013755</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AA52" t="n">
         <v>0.0362332308761499</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>3370</v>
       </c>
       <c r="AD52" t="s">
         <v>38</v>
       </c>
       <c r="AE52" t="s">
-        <v>3373</v>
-      </c>
-      <c r="AF52" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG52" t="s">
-        <v>3373</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ52" t="s">
-        <v>3483</v>
+        <v>3370</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>3480</v>
       </c>
     </row>
   </sheetData>
@@ -17348,37 +17216,28 @@
         <v>3332</v>
       </c>
       <c r="V1" t="s">
-        <v>3484</v>
+        <v>55</v>
       </c>
       <c r="W1" t="s">
-        <v>3485</v>
+        <v>3335</v>
       </c>
       <c r="X1" t="s">
-        <v>3486</v>
+        <v>3336</v>
       </c>
       <c r="Y1" t="s">
-        <v>3487</v>
+        <v>3337</v>
       </c>
       <c r="Z1" t="s">
-        <v>3488</v>
+        <v>36</v>
       </c>
       <c r="AA1" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="AB1" t="s">
-        <v>3340</v>
+        <v>3481</v>
       </c>
       <c r="AC1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3341</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3489</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3344</v>
       </c>
     </row>
     <row r="2">
@@ -17386,10 +17245,10 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>3490</v>
+        <v>3482</v>
       </c>
       <c r="C2" t="s">
-        <v>3473</v>
+        <v>3470</v>
       </c>
       <c r="D2" t="n">
         <v>72104</v>
@@ -17446,37 +17305,28 @@
         <v>71917</v>
       </c>
       <c r="V2" t="n">
-        <v>-24.723650404748</v>
+        <v>-1.81749613747093</v>
       </c>
       <c r="W2" t="n">
-        <v>-9.33685176276743</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-8.14997445965351</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-7.97391359859409</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-12.5096066190951</v>
+        <v>0.120914345461454</v>
+      </c>
+      <c r="X2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>38</v>
       </c>
       <c r="AA2" t="s">
         <v>38</v>
       </c>
-      <c r="AB2" t="s">
-        <v>38</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3491</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="3">
@@ -17484,10 +17334,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>3492</v>
+        <v>3484</v>
       </c>
       <c r="C3" t="s">
-        <v>3459</v>
+        <v>3456</v>
       </c>
       <c r="D3" t="n">
         <v>76139</v>
@@ -17544,37 +17394,28 @@
         <v>75412</v>
       </c>
       <c r="V3" t="n">
-        <v>-21.1072158286051</v>
+        <v>-0.312300958454043</v>
       </c>
       <c r="W3" t="n">
-        <v>-11.9089992032295</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-7.46494963469473</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-11.2852703464417</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-9.40332467875459</v>
+        <v>0.0225651591175057</v>
+      </c>
+      <c r="X3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>38</v>
       </c>
       <c r="AA3" t="s">
         <v>38</v>
       </c>
-      <c r="AB3" t="s">
-        <v>38</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3493</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="4">
@@ -17582,10 +17423,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>3494</v>
+        <v>3486</v>
       </c>
       <c r="C4" t="s">
-        <v>3427</v>
+        <v>3424</v>
       </c>
       <c r="D4" t="n">
         <v>123980</v>
@@ -17642,37 +17483,28 @@
         <v>123987</v>
       </c>
       <c r="V4" t="n">
-        <v>10.4873633253355</v>
+        <v>0.485899196416517</v>
       </c>
       <c r="W4" t="n">
-        <v>6.76996757513496</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.55003472103215</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7.61323069011072</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.0789986454059</v>
+        <v>0.0651011667219734</v>
+      </c>
+      <c r="X4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>38</v>
       </c>
       <c r="AA4" t="s">
         <v>38</v>
       </c>
-      <c r="AB4" t="s">
-        <v>38</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3495</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="5">
@@ -17680,10 +17512,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>3496</v>
+        <v>3488</v>
       </c>
       <c r="C5" t="s">
-        <v>3497</v>
+        <v>3489</v>
       </c>
       <c r="D5" t="n">
         <v>33927</v>
@@ -17740,37 +17572,28 @@
         <v>34569</v>
       </c>
       <c r="V5" t="n">
-        <v>7.68753643692801</v>
+        <v>0.0989999733454292</v>
       </c>
       <c r="W5" t="n">
-        <v>6.98556216983549</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.87560627782108</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6.23599690887711</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.30875169005616</v>
+        <v>0.0159998807382147</v>
+      </c>
+      <c r="X5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>38</v>
       </c>
       <c r="AA5" t="s">
         <v>38</v>
       </c>
-      <c r="AB5" t="s">
-        <v>38</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3498</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="6">
@@ -17778,10 +17601,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>3499</v>
+        <v>3491</v>
       </c>
       <c r="C6" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="D6" t="n">
         <v>67971</v>
@@ -17838,37 +17661,28 @@
         <v>66142</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.08789581250921</v>
+        <v>-0.172000065180725</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.68533681834879</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.37439951530751</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-4.16742036662453</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-6.3799434797683</v>
+        <v>0.0308410440635351</v>
+      </c>
+      <c r="X6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>38</v>
       </c>
       <c r="AA6" t="s">
         <v>38</v>
       </c>
-      <c r="AB6" t="s">
-        <v>38</v>
+      <c r="AB6" t="n">
+        <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3500</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="7">
@@ -17876,10 +17690,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>3501</v>
+        <v>3493</v>
       </c>
       <c r="C7" t="s">
-        <v>3470</v>
+        <v>3467</v>
       </c>
       <c r="D7" t="n">
         <v>92343</v>
@@ -17936,37 +17750,28 @@
         <v>92456</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.45554373050545</v>
+        <v>-0.763151526534408</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.81825950293695</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-2.24219947165442</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-2.76616105205578</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-5.74109633297777</v>
+        <v>0.18229535783167</v>
+      </c>
+      <c r="X7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>38</v>
       </c>
       <c r="AA7" t="s">
         <v>38</v>
       </c>
-      <c r="AB7" t="s">
-        <v>38</v>
+      <c r="AB7" t="n">
+        <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>3501</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="8">
@@ -17974,7 +17779,7 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>3502</v>
+        <v>3494</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
@@ -18034,37 +17839,28 @@
         <v>104277</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.63340226019959</v>
+        <v>-0.0821519376067908</v>
       </c>
       <c r="W8" t="n">
-        <v>-4.874488093577</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.663907012328</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-2.60126908378597</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.79038082073724</v>
+        <v>0.019339777507998</v>
+      </c>
+      <c r="X8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>38</v>
       </c>
       <c r="AA8" t="s">
         <v>38</v>
       </c>
-      <c r="AB8" t="s">
-        <v>38</v>
+      <c r="AB8" t="n">
+        <v>0</v>
       </c>
       <c r="AC8" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3503</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="9">
@@ -18072,7 +17868,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>3504</v>
+        <v>3496</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -18132,37 +17928,28 @@
         <v>113379</v>
       </c>
       <c r="V9" t="n">
-        <v>4.68351672814096</v>
+        <v>0.138318732841764</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56135545138351</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4.94911694807653</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.62642851343789</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.65374673192182</v>
+        <v>0.0405545517272401</v>
+      </c>
+      <c r="X9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>38</v>
       </c>
       <c r="AA9" t="s">
         <v>38</v>
       </c>
-      <c r="AB9" t="s">
-        <v>38</v>
+      <c r="AB9" t="n">
+        <v>0</v>
       </c>
       <c r="AC9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>3505</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="10">
@@ -18170,10 +17957,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>3506</v>
+        <v>3498</v>
       </c>
       <c r="C10" t="s">
-        <v>3507</v>
+        <v>3499</v>
       </c>
       <c r="D10" t="n">
         <v>33927</v>
@@ -18230,37 +18017,28 @@
         <v>38695</v>
       </c>
       <c r="V10" t="n">
-        <v>5.05954871055187</v>
+        <v>0.182022514588102</v>
       </c>
       <c r="W10" t="n">
-        <v>4.17824644757272</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.71006719646124</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.22588759667802</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.55240224559516</v>
+        <v>0.0570082399376852</v>
+      </c>
+      <c r="X10" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>38</v>
       </c>
       <c r="AA10" t="s">
         <v>38</v>
       </c>
-      <c r="AB10" t="s">
-        <v>38</v>
+      <c r="AB10" t="n">
+        <v>0</v>
       </c>
       <c r="AC10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>3508</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="11">
@@ -18268,10 +18046,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>3509</v>
+        <v>3501</v>
       </c>
       <c r="C11" t="s">
-        <v>3510</v>
+        <v>3502</v>
       </c>
       <c r="D11" t="n">
         <v>119938</v>
@@ -18328,37 +18106,28 @@
         <v>115405</v>
       </c>
       <c r="V11" t="n">
-        <v>3.00302712515959</v>
+        <v>0.0664764679977411</v>
       </c>
       <c r="W11" t="n">
-        <v>3.50684046179651</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.75303728381366</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.54281452541761</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.27481913697529</v>
+        <v>0.0244134821953691</v>
+      </c>
+      <c r="X11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>38</v>
       </c>
       <c r="AA11" t="s">
         <v>38</v>
       </c>
-      <c r="AB11" t="s">
-        <v>38</v>
+      <c r="AB11" t="n">
+        <v>0.000609756097560976</v>
       </c>
       <c r="AC11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.000609756097560976</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>3511</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="12">
@@ -18366,10 +18135,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>3512</v>
+        <v>3504</v>
       </c>
       <c r="C12" t="s">
-        <v>3473</v>
+        <v>3470</v>
       </c>
       <c r="D12" t="n">
         <v>67971</v>
@@ -18426,37 +18195,28 @@
         <v>75977</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.63987752152098</v>
+        <v>-0.422194735823153</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.02950099180463</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.13772897202479</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-3.25115761075567</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-2.95328687711416</v>
+        <v>0.158672780786247</v>
+      </c>
+      <c r="X12" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>38</v>
       </c>
       <c r="AA12" t="s">
         <v>38</v>
       </c>
-      <c r="AB12" t="s">
-        <v>38</v>
+      <c r="AB12" t="n">
+        <v>0.000609756097560976</v>
       </c>
       <c r="AC12" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.000609756097560976</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>3513</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="13">
@@ -18464,10 +18224,10 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>3514</v>
+        <v>3506</v>
       </c>
       <c r="C13" t="s">
-        <v>3515</v>
+        <v>3507</v>
       </c>
       <c r="D13" t="n">
         <v>67971</v>
@@ -18524,37 +18284,28 @@
         <v>53099</v>
       </c>
       <c r="V13" t="n">
-        <v>2.29451921818777</v>
+        <v>0.144739074225574</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.85426167214443</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.10371265684357</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.44245650304167</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97318753141707</v>
+        <v>0.0969851787044326</v>
+      </c>
+      <c r="X13" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>38</v>
       </c>
       <c r="AA13" t="s">
         <v>38</v>
       </c>
-      <c r="AB13" t="s">
-        <v>38</v>
+      <c r="AB13" t="n">
+        <v>0.0057141722991834</v>
       </c>
       <c r="AC13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.0057141722991834</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>3514</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="14">
@@ -18562,10 +18313,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>3516</v>
+        <v>3508</v>
       </c>
       <c r="C14" t="s">
-        <v>3517</v>
+        <v>3509</v>
       </c>
       <c r="D14" t="n">
         <v>67971</v>
@@ -18622,37 +18373,28 @@
         <v>99219</v>
       </c>
       <c r="V14" t="n">
-        <v>2.85882315596124</v>
+        <v>0.157396536257213</v>
       </c>
       <c r="W14" t="n">
-        <v>2.63389367830187</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.02536358900773</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.02081844768708</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-0.287642024442485</v>
+        <v>0.0852462914336155</v>
+      </c>
+      <c r="X14" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>38</v>
       </c>
       <c r="AA14" t="s">
         <v>38</v>
       </c>
-      <c r="AB14" t="s">
-        <v>38</v>
+      <c r="AB14" t="n">
+        <v>0.00724094881398252</v>
       </c>
       <c r="AC14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.00724094881398252</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>3518</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="15">
@@ -18660,10 +18402,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>3519</v>
+        <v>3511</v>
       </c>
       <c r="C15" t="s">
-        <v>3427</v>
+        <v>3424</v>
       </c>
       <c r="D15" t="n">
         <v>121030</v>
@@ -18720,37 +18462,28 @@
         <v>129481</v>
       </c>
       <c r="V15" t="n">
-        <v>1.76866533223154</v>
+        <v>0.101977455061516</v>
       </c>
       <c r="W15" t="n">
-        <v>1.90713688041994</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.68542656636327</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.518516216767306</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.4030736659468</v>
+        <v>0.0554362711273935</v>
+      </c>
+      <c r="X15" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>38</v>
       </c>
       <c r="AA15" t="s">
         <v>38</v>
       </c>
-      <c r="AB15" t="s">
-        <v>38</v>
+      <c r="AB15" t="n">
+        <v>0.00905752753977968</v>
       </c>
       <c r="AC15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.00905752753977968</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>3520</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="16">
@@ -18758,10 +18491,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>3521</v>
+        <v>3513</v>
       </c>
       <c r="C16" t="s">
-        <v>3367</v>
+        <v>3364</v>
       </c>
       <c r="D16" t="n">
         <v>1028</v>
@@ -18818,37 +18551,28 @@
         <v>119825</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7591604848746</v>
+        <v>-0.0615241065206021</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.35824305034548</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.905899719128602</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>-2.63300539954589</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-1.54798621652823</v>
+        <v>0.0358980887735083</v>
+      </c>
+      <c r="X16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>38</v>
       </c>
       <c r="AA16" t="s">
         <v>38</v>
       </c>
-      <c r="AB16" t="s">
-        <v>38</v>
+      <c r="AB16" t="n">
+        <v>0.0108711043731668</v>
       </c>
       <c r="AC16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.0108711043731668</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>3522</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="17">
@@ -18856,7 +18580,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>3523</v>
+        <v>3515</v>
       </c>
       <c r="C17" t="s">
         <v>34</v>
@@ -18916,37 +18640,28 @@
         <v>109948</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1035737426313</v>
+        <v>0.114523774147851</v>
       </c>
       <c r="W17" t="n">
-        <v>1.95415182356174</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.62082160759392</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.791693794540917</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.45142641003331</v>
+        <v>0.0699778346804151</v>
+      </c>
+      <c r="X17" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>38</v>
       </c>
       <c r="AA17" t="s">
         <v>38</v>
       </c>
-      <c r="AB17" t="s">
-        <v>38</v>
+      <c r="AB17" t="n">
+        <v>0.0149094594571441</v>
       </c>
       <c r="AC17" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.0149094594571441</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>3524</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="18">
@@ -18954,10 +18669,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>3525</v>
+        <v>3517</v>
       </c>
       <c r="C18" t="s">
-        <v>3526</v>
+        <v>3518</v>
       </c>
       <c r="D18" t="n">
         <v>167475</v>
@@ -19014,37 +18729,28 @@
         <v>81844</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1796675260916</v>
+        <v>-0.0987907419722788</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.185981706294465</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.93256667311224</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-1.66193515895128</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.64090364856823</v>
+        <v>0.133219873870777</v>
+      </c>
+      <c r="X18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>38</v>
       </c>
       <c r="AA18" t="s">
         <v>38</v>
       </c>
-      <c r="AB18" t="s">
-        <v>38</v>
+      <c r="AB18" t="n">
+        <v>0.0158244331335016</v>
       </c>
       <c r="AC18" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.0158244331335016</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>3527</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="19">
@@ -19052,10 +18758,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>3528</v>
+        <v>3520</v>
       </c>
       <c r="C19" t="s">
-        <v>3529</v>
+        <v>3521</v>
       </c>
       <c r="D19" t="n">
         <v>424278</v>
@@ -19112,37 +18818,28 @@
         <v>67711</v>
       </c>
       <c r="V19" t="n">
-        <v>2.95505608686015</v>
+        <v>0.338452573621702</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.761960351018717</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.28944716367268</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>-0.447711578636346</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.43730105368788</v>
+        <v>0.309520319864456</v>
+      </c>
+      <c r="X19" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>38</v>
       </c>
       <c r="AA19" t="s">
         <v>38</v>
       </c>
-      <c r="AB19" t="s">
-        <v>38</v>
+      <c r="AB19" t="n">
+        <v>0.0199714377860725</v>
       </c>
       <c r="AC19" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.0199714377860725</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>3528</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="20">
@@ -19150,10 +18847,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>3530</v>
+        <v>3522</v>
       </c>
       <c r="C20" t="s">
-        <v>3531</v>
+        <v>3523</v>
       </c>
       <c r="D20" t="n">
         <v>48147</v>
@@ -19210,37 +18907,28 @@
         <v>94998</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.60442502076951</v>
+        <v>-0.0871636205786345</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0180126426742635</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.83111774456902</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.760602272729469</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.761067731174366</v>
+        <v>0.0742657153821866</v>
+      </c>
+      <c r="X20" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>38</v>
       </c>
       <c r="AA20" t="s">
         <v>38</v>
       </c>
-      <c r="AB20" t="s">
-        <v>38</v>
+      <c r="AB20" t="n">
+        <v>0.0199789695057834</v>
       </c>
       <c r="AC20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.0199789695057834</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>3532</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="21">
@@ -19248,10 +18936,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>3533</v>
+        <v>3525</v>
       </c>
       <c r="C21" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="D21" t="n">
         <v>53107</v>
@@ -19308,37 +18996,28 @@
         <v>67652</v>
       </c>
       <c r="V21" t="n">
-        <v>0.161933347194957</v>
+        <v>0.137138928872345</v>
       </c>
       <c r="W21" t="n">
-        <v>0.763280643964144</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.86430989702484</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>3.19355406187451</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.69882353844441</v>
+        <v>0.106656737135314</v>
+      </c>
+      <c r="X21" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>38</v>
       </c>
       <c r="AA21" t="s">
         <v>38</v>
       </c>
-      <c r="AB21" t="s">
-        <v>38</v>
+      <c r="AB21" t="n">
+        <v>0.0199789695057834</v>
       </c>
       <c r="AC21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.0199789695057834</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>3534</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="22">
@@ -19346,10 +19025,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>3535</v>
+        <v>3527</v>
       </c>
       <c r="C22" t="s">
-        <v>3400</v>
+        <v>3397</v>
       </c>
       <c r="D22" t="n">
         <v>1028</v>
@@ -19406,37 +19085,28 @@
         <v>100413</v>
       </c>
       <c r="V22" t="n">
-        <v>2.65151438431853</v>
+        <v>0.0887722377595604</v>
       </c>
       <c r="W22" t="n">
-        <v>2.87067505096908</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.413722191610097</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.931035096114204</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.999100059805543</v>
+        <v>0.0512284528420068</v>
+      </c>
+      <c r="X22" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>38</v>
       </c>
       <c r="AA22" t="s">
         <v>38</v>
       </c>
-      <c r="AB22" t="s">
-        <v>38</v>
+      <c r="AB22" t="n">
+        <v>0.0207049344859086</v>
       </c>
       <c r="AC22" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.0207049344859086</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>3536</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="23">
@@ -19444,10 +19114,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>3537</v>
+        <v>3529</v>
       </c>
       <c r="C23" t="s">
-        <v>3538</v>
+        <v>3530</v>
       </c>
       <c r="D23" t="n">
         <v>115855</v>
@@ -19504,37 +19174,28 @@
         <v>36319</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.34830743499455</v>
+        <v>-0.0630855015738035</v>
       </c>
       <c r="W23" t="n">
-        <v>2.00621091699468</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.902368007432807</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>-0.737508650572333</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.635278463094322</v>
+        <v>0.0981215110565109</v>
+      </c>
+      <c r="X23" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>38</v>
       </c>
       <c r="AA23" t="s">
         <v>38</v>
       </c>
-      <c r="AB23" t="s">
-        <v>38</v>
+      <c r="AB23" t="n">
+        <v>0.022682577085575</v>
       </c>
       <c r="AC23" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.022682577085575</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>3539</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="24">
@@ -19542,10 +19203,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>3540</v>
+        <v>3532</v>
       </c>
       <c r="C24" t="s">
-        <v>3541</v>
+        <v>3533</v>
       </c>
       <c r="D24" t="n">
         <v>1028</v>
@@ -19602,37 +19263,28 @@
         <v>54851</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.19914865674098</v>
+        <v>-0.0922186518401685</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.94039250726233</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-2.1961215432342</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>-0.493498843558162</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-1.73853981675009</v>
+        <v>0.0518512621177221</v>
+      </c>
+      <c r="X24" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>38</v>
       </c>
       <c r="AA24" t="s">
         <v>38</v>
       </c>
-      <c r="AB24" t="s">
-        <v>38</v>
+      <c r="AB24" t="n">
+        <v>0.0252792539678322</v>
       </c>
       <c r="AC24" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.0252792539678322</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>3542</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="25">
@@ -19640,10 +19292,10 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>3543</v>
+        <v>3535</v>
       </c>
       <c r="C25" t="s">
-        <v>3541</v>
+        <v>3533</v>
       </c>
       <c r="D25" t="n">
         <v>1028</v>
@@ -19700,37 +19352,28 @@
         <v>138694</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.669283631753817</v>
+        <v>-0.0726815079480141</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.17705274278064</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.30808180488312</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>-0.367531192747194</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>-3.04752923055694</v>
+        <v>0.0890317377458603</v>
+      </c>
+      <c r="X25" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>38</v>
       </c>
       <c r="AA25" t="s">
         <v>38</v>
       </c>
-      <c r="AB25" t="s">
-        <v>38</v>
+      <c r="AB25" t="n">
+        <v>0.0256049627254112</v>
       </c>
       <c r="AC25" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0.0256049627254112</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>3544</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="26">
@@ -19738,10 +19381,10 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>3545</v>
+        <v>3537</v>
       </c>
       <c r="C26" t="s">
-        <v>3400</v>
+        <v>3397</v>
       </c>
       <c r="D26" t="n">
         <v>33927</v>
@@ -19798,37 +19441,28 @@
         <v>136680</v>
       </c>
       <c r="V26" t="n">
-        <v>2.92983512245812</v>
+        <v>0.0940184187678562</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.153485171271621</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-0.0950821454322473</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.387174312514051</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.60659285481118</v>
+        <v>0.0643517491178607</v>
+      </c>
+      <c r="X26" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>38</v>
       </c>
       <c r="AA26" t="s">
         <v>38</v>
       </c>
-      <c r="AB26" t="s">
-        <v>38</v>
+      <c r="AB26" t="n">
+        <v>0.0346927247921523</v>
       </c>
       <c r="AC26" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.0346927247921523</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>3546</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="27">
@@ -19836,10 +19470,10 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>3547</v>
+        <v>3539</v>
       </c>
       <c r="C27" t="s">
-        <v>3441</v>
+        <v>3438</v>
       </c>
       <c r="D27" t="n">
         <v>53107</v>
@@ -19896,37 +19530,28 @@
         <v>48763</v>
       </c>
       <c r="V27" t="n">
-        <v>0.600448299146954</v>
+        <v>-0.150590955520819</v>
       </c>
       <c r="W27" t="n">
-        <v>-2.13173853150876</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.17701827527388</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>-2.67121764667459</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>-1.00135843900598</v>
+        <v>0.174325747997282</v>
+      </c>
+      <c r="X27" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>38</v>
       </c>
       <c r="AA27" t="s">
         <v>38</v>
       </c>
-      <c r="AB27" t="s">
-        <v>38</v>
+      <c r="AB27" t="n">
+        <v>0.0411054006954977</v>
       </c>
       <c r="AC27" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0.0411054006954977</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>3548</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="28">
@@ -19934,10 +19559,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>3549</v>
+        <v>3541</v>
       </c>
       <c r="C28" t="s">
-        <v>3550</v>
+        <v>3542</v>
       </c>
       <c r="D28" t="n">
         <v>1028</v>
@@ -19994,37 +19619,28 @@
         <v>102612</v>
       </c>
       <c r="V28" t="n">
-        <v>-1.01793097238975</v>
+        <v>0.0402302202531902</v>
       </c>
       <c r="W28" t="n">
-        <v>2.40132491482855</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.27738633921318</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0.153881602001573</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.58162813514089</v>
+        <v>0.0547720380141851</v>
+      </c>
+      <c r="X28" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>38</v>
       </c>
       <c r="AA28" t="s">
         <v>38</v>
       </c>
-      <c r="AB28" t="s">
-        <v>38</v>
+      <c r="AB28" t="n">
+        <v>0.048231204635964</v>
       </c>
       <c r="AC28" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0.048231204635964</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>3551</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="29">
@@ -20032,10 +19648,10 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>3552</v>
+        <v>3544</v>
       </c>
       <c r="C29" t="s">
-        <v>3553</v>
+        <v>3545</v>
       </c>
       <c r="D29" t="n">
         <v>206460</v>
@@ -20092,37 +19708,28 @@
         <v>59003</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01679452806216</v>
+        <v>0.0744756031164287</v>
       </c>
       <c r="W29" t="n">
-        <v>-2.01011410543695</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.693350005399062</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.73904635437927</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.12416477594196</v>
+        <v>0.102955650159861</v>
+      </c>
+      <c r="X29" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>38</v>
       </c>
       <c r="AA29" t="s">
         <v>38</v>
       </c>
-      <c r="AB29" t="s">
-        <v>38</v>
+      <c r="AB29" t="n">
+        <v>0.048848274855543</v>
       </c>
       <c r="AC29" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0.048848274855543</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>3554</v>
+        <v>3546</v>
       </c>
     </row>
   </sheetData>
@@ -20153,34 +19760,34 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3555</v>
+        <v>3547</v>
       </c>
       <c r="G1" t="s">
         <v>1865</v>
       </c>
       <c r="H1" t="s">
-        <v>3556</v>
+        <v>3548</v>
       </c>
       <c r="I1" t="s">
-        <v>3557</v>
+        <v>3549</v>
       </c>
       <c r="J1" t="s">
         <v>1918</v>
       </c>
       <c r="K1" t="s">
-        <v>3558</v>
+        <v>3550</v>
       </c>
       <c r="L1" t="s">
-        <v>3559</v>
+        <v>3551</v>
       </c>
       <c r="M1" t="s">
-        <v>3560</v>
+        <v>3552</v>
       </c>
       <c r="N1" t="s">
-        <v>3561</v>
+        <v>3553</v>
       </c>
       <c r="O1" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="P1" t="s">
         <v>3332</v>
@@ -20200,33 +19807,33 @@
         <v>885</v>
       </c>
       <c r="E2" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F2" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G2" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3565</v>
+        <v>3557</v>
       </c>
       <c r="K2" t="s">
-        <v>3566</v>
+        <v>3558</v>
       </c>
       <c r="L2" t="s">
-        <v>3565</v>
+        <v>3557</v>
       </c>
       <c r="M2" t="s">
-        <v>3567</v>
+        <v>3559</v>
       </c>
       <c r="N2" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O2" t="s">
-        <v>3569</v>
+        <v>3561</v>
       </c>
       <c r="P2" t="n">
         <v>33635</v>
@@ -20246,33 +19853,33 @@
         <v>771</v>
       </c>
       <c r="E3" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F3" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G3" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3496</v>
+        <v>3488</v>
       </c>
       <c r="K3" t="s">
-        <v>3570</v>
+        <v>3562</v>
       </c>
       <c r="L3" t="s">
-        <v>3496</v>
+        <v>3488</v>
       </c>
       <c r="M3" t="s">
-        <v>3571</v>
+        <v>3563</v>
       </c>
       <c r="N3" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O3" t="s">
-        <v>3498</v>
+        <v>3490</v>
       </c>
       <c r="P3" t="n">
         <v>35640</v>
@@ -20292,33 +19899,33 @@
         <v>2130</v>
       </c>
       <c r="E4" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F4" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G4" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3537</v>
+        <v>3529</v>
       </c>
       <c r="K4" t="s">
-        <v>3572</v>
+        <v>3564</v>
       </c>
       <c r="L4" t="s">
-        <v>3537</v>
+        <v>3529</v>
       </c>
       <c r="M4" t="s">
-        <v>3573</v>
+        <v>3565</v>
       </c>
       <c r="N4" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O4" t="s">
-        <v>3539</v>
+        <v>3531</v>
       </c>
       <c r="P4" t="n">
         <v>37444</v>
@@ -20338,33 +19945,33 @@
         <v>672</v>
       </c>
       <c r="E5" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F5" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G5" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3506</v>
+        <v>3498</v>
       </c>
       <c r="K5" t="s">
-        <v>3574</v>
+        <v>3566</v>
       </c>
       <c r="L5" t="s">
-        <v>3506</v>
+        <v>3498</v>
       </c>
       <c r="M5" t="s">
-        <v>3575</v>
+        <v>3567</v>
       </c>
       <c r="N5" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O5" t="s">
-        <v>3508</v>
+        <v>3500</v>
       </c>
       <c r="P5" t="n">
         <v>39150</v>
@@ -20384,33 +19991,33 @@
         <v>5607</v>
       </c>
       <c r="E6" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F6" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G6" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3577</v>
+        <v>3569</v>
       </c>
       <c r="K6" t="s">
-        <v>3578</v>
+        <v>3570</v>
       </c>
       <c r="L6" t="s">
-        <v>3577</v>
+        <v>3569</v>
       </c>
       <c r="M6" t="s">
-        <v>3579</v>
+        <v>3571</v>
       </c>
       <c r="N6" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O6" t="s">
-        <v>3580</v>
+        <v>3572</v>
       </c>
       <c r="P6" t="n">
         <v>42887</v>
@@ -20430,33 +20037,33 @@
         <v>2040</v>
       </c>
       <c r="E7" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F7" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G7" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3581</v>
+        <v>3573</v>
       </c>
       <c r="K7" t="s">
-        <v>3582</v>
+        <v>3574</v>
       </c>
       <c r="L7" t="s">
-        <v>3581</v>
+        <v>3573</v>
       </c>
       <c r="M7" t="s">
-        <v>3583</v>
+        <v>3575</v>
       </c>
       <c r="N7" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O7" t="s">
-        <v>3585</v>
+        <v>3577</v>
       </c>
       <c r="P7" t="n">
         <v>46948</v>
@@ -20476,33 +20083,33 @@
         <v>1818</v>
       </c>
       <c r="E8" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F8" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G8" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3547</v>
+        <v>3539</v>
       </c>
       <c r="K8" t="s">
-        <v>3586</v>
+        <v>3578</v>
       </c>
       <c r="L8" t="s">
-        <v>3547</v>
+        <v>3539</v>
       </c>
       <c r="M8" t="s">
-        <v>3587</v>
+        <v>3579</v>
       </c>
       <c r="N8" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O8" t="s">
-        <v>3548</v>
+        <v>3540</v>
       </c>
       <c r="P8" t="n">
         <v>49672</v>
@@ -20522,33 +20129,33 @@
         <v>1878</v>
       </c>
       <c r="E9" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F9" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G9" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3588</v>
+        <v>3580</v>
       </c>
       <c r="K9" t="s">
-        <v>3589</v>
+        <v>3581</v>
       </c>
       <c r="L9" t="s">
-        <v>3588</v>
+        <v>3580</v>
       </c>
       <c r="M9" t="s">
-        <v>3590</v>
+        <v>3582</v>
       </c>
       <c r="N9" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O9" t="s">
-        <v>3591</v>
+        <v>3583</v>
       </c>
       <c r="P9" t="n">
         <v>52050</v>
@@ -20568,30 +20175,30 @@
         <v>948</v>
       </c>
       <c r="E10" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F10" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G10" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3514</v>
+        <v>3506</v>
       </c>
       <c r="K10" t="s">
-        <v>3592</v>
+        <v>3584</v>
       </c>
       <c r="L10" t="s">
-        <v>3514</v>
+        <v>3506</v>
       </c>
       <c r="M10" t="s">
-        <v>3593</v>
+        <v>3585</v>
       </c>
       <c r="N10" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
@@ -20612,33 +20219,33 @@
         <v>999</v>
       </c>
       <c r="E11" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F11" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G11" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3540</v>
+        <v>3532</v>
       </c>
       <c r="K11" t="s">
-        <v>3594</v>
+        <v>3586</v>
       </c>
       <c r="L11" t="s">
-        <v>3540</v>
+        <v>3532</v>
       </c>
       <c r="M11" t="s">
-        <v>3595</v>
+        <v>3587</v>
       </c>
       <c r="N11" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O11" t="s">
-        <v>3542</v>
+        <v>3534</v>
       </c>
       <c r="P11" t="n">
         <v>55350</v>
@@ -20658,33 +20265,33 @@
         <v>2142</v>
       </c>
       <c r="E12" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F12" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G12" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>3596</v>
+        <v>3588</v>
       </c>
       <c r="K12" t="s">
-        <v>3597</v>
+        <v>3589</v>
       </c>
       <c r="L12" t="s">
-        <v>3596</v>
+        <v>3588</v>
       </c>
       <c r="M12" t="s">
-        <v>3598</v>
+        <v>3590</v>
       </c>
       <c r="N12" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O12" t="s">
-        <v>3599</v>
+        <v>3591</v>
       </c>
       <c r="P12" t="n">
         <v>57720</v>
@@ -20704,33 +20311,33 @@
         <v>3441</v>
       </c>
       <c r="E13" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F13" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G13" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3552</v>
+        <v>3544</v>
       </c>
       <c r="K13" t="s">
-        <v>3600</v>
+        <v>3592</v>
       </c>
       <c r="L13" t="s">
-        <v>3552</v>
+        <v>3544</v>
       </c>
       <c r="M13" t="s">
-        <v>3601</v>
+        <v>3593</v>
       </c>
       <c r="N13" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O13" t="s">
-        <v>3554</v>
+        <v>3546</v>
       </c>
       <c r="P13" t="n">
         <v>60843</v>
@@ -20750,33 +20357,33 @@
         <v>1197</v>
       </c>
       <c r="E14" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F14" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G14" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3602</v>
+        <v>3594</v>
       </c>
       <c r="K14" t="s">
-        <v>3603</v>
+        <v>3595</v>
       </c>
       <c r="L14" t="s">
-        <v>3602</v>
+        <v>3594</v>
       </c>
       <c r="M14" t="s">
-        <v>3604</v>
+        <v>3596</v>
       </c>
       <c r="N14" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O14" t="s">
-        <v>3605</v>
+        <v>3597</v>
       </c>
       <c r="P14" t="n">
         <v>63559</v>
@@ -20796,33 +20403,33 @@
         <v>1398</v>
       </c>
       <c r="E15" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F15" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G15" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3606</v>
+        <v>3598</v>
       </c>
       <c r="K15" t="s">
-        <v>3607</v>
+        <v>3599</v>
       </c>
       <c r="L15" t="s">
-        <v>3606</v>
+        <v>3598</v>
       </c>
       <c r="M15" t="s">
-        <v>3608</v>
+        <v>3600</v>
       </c>
       <c r="N15" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O15" t="s">
-        <v>3609</v>
+        <v>3601</v>
       </c>
       <c r="P15" t="n">
         <v>65160</v>
@@ -20842,33 +20449,33 @@
         <v>1215</v>
       </c>
       <c r="E16" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F16" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G16" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3499</v>
+        <v>3491</v>
       </c>
       <c r="K16" t="s">
-        <v>3610</v>
+        <v>3602</v>
       </c>
       <c r="L16" t="s">
-        <v>3499</v>
+        <v>3491</v>
       </c>
       <c r="M16" t="s">
-        <v>3611</v>
+        <v>3603</v>
       </c>
       <c r="N16" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O16" t="s">
-        <v>3500</v>
+        <v>3492</v>
       </c>
       <c r="P16" t="n">
         <v>66849</v>
@@ -20888,33 +20495,33 @@
         <v>1818</v>
       </c>
       <c r="E17" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F17" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G17" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3533</v>
+        <v>3525</v>
       </c>
       <c r="K17" t="s">
-        <v>3612</v>
+        <v>3604</v>
       </c>
       <c r="L17" t="s">
-        <v>3533</v>
+        <v>3525</v>
       </c>
       <c r="M17" t="s">
-        <v>3608</v>
+        <v>3600</v>
       </c>
       <c r="N17" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O17" t="s">
-        <v>3534</v>
+        <v>3526</v>
       </c>
       <c r="P17" t="n">
         <v>68640</v>
@@ -20934,30 +20541,30 @@
         <v>363</v>
       </c>
       <c r="E18" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F18" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G18" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3613</v>
+        <v>3605</v>
       </c>
       <c r="K18" t="s">
-        <v>3614</v>
+        <v>3606</v>
       </c>
       <c r="L18" t="s">
-        <v>3613</v>
+        <v>3605</v>
       </c>
       <c r="M18" t="s">
-        <v>3615</v>
+        <v>3607</v>
       </c>
       <c r="N18" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O18"/>
       <c r="P18" t="n">
@@ -20978,30 +20585,30 @@
         <v>1599</v>
       </c>
       <c r="E19" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F19" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G19" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3616</v>
+        <v>3608</v>
       </c>
       <c r="K19" t="s">
-        <v>3617</v>
+        <v>3609</v>
       </c>
       <c r="L19" t="s">
-        <v>3616</v>
+        <v>3608</v>
       </c>
       <c r="M19" t="s">
-        <v>3593</v>
+        <v>3585</v>
       </c>
       <c r="N19" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O19"/>
       <c r="P19" t="n">
@@ -21022,33 +20629,33 @@
         <v>2208</v>
       </c>
       <c r="E20" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F20" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G20" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3490</v>
+        <v>3482</v>
       </c>
       <c r="K20" t="s">
-        <v>3618</v>
+        <v>3610</v>
       </c>
       <c r="L20" t="s">
-        <v>3490</v>
+        <v>3482</v>
       </c>
       <c r="M20" t="s">
-        <v>3619</v>
+        <v>3611</v>
       </c>
       <c r="N20" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O20" t="s">
-        <v>3491</v>
+        <v>3483</v>
       </c>
       <c r="P20" t="n">
         <v>73140</v>
@@ -21068,30 +20675,30 @@
         <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F21" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G21" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3620</v>
+        <v>3612</v>
       </c>
       <c r="K21" t="s">
-        <v>3621</v>
+        <v>3613</v>
       </c>
       <c r="L21" t="s">
-        <v>3620</v>
+        <v>3612</v>
       </c>
       <c r="M21" t="s">
-        <v>3593</v>
+        <v>3585</v>
       </c>
       <c r="N21" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O21"/>
       <c r="P21" t="n">
@@ -21112,33 +20719,33 @@
         <v>366</v>
       </c>
       <c r="E22" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F22" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G22" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>3492</v>
+        <v>3484</v>
       </c>
       <c r="K22" t="s">
-        <v>3622</v>
+        <v>3614</v>
       </c>
       <c r="L22" t="s">
-        <v>3492</v>
+        <v>3484</v>
       </c>
       <c r="M22" t="s">
-        <v>3623</v>
+        <v>3615</v>
       </c>
       <c r="N22" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O22" t="s">
-        <v>3493</v>
+        <v>3485</v>
       </c>
       <c r="P22" t="n">
         <v>75594</v>
@@ -21158,33 +20765,33 @@
         <v>1218</v>
       </c>
       <c r="E23" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F23" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G23" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3512</v>
+        <v>3504</v>
       </c>
       <c r="K23" t="s">
-        <v>3624</v>
+        <v>3616</v>
       </c>
       <c r="L23" t="s">
-        <v>3512</v>
+        <v>3504</v>
       </c>
       <c r="M23" t="s">
-        <v>3608</v>
+        <v>3600</v>
       </c>
       <c r="N23" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O23" t="s">
-        <v>3513</v>
+        <v>3505</v>
       </c>
       <c r="P23" t="n">
         <v>76706</v>
@@ -21204,33 +20811,33 @@
         <v>924</v>
       </c>
       <c r="E24" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F24" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G24" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>3625</v>
+        <v>3617</v>
       </c>
       <c r="K24" t="s">
-        <v>3626</v>
+        <v>3618</v>
       </c>
       <c r="L24" t="s">
-        <v>3625</v>
+        <v>3617</v>
       </c>
       <c r="M24" t="s">
-        <v>3608</v>
+        <v>3600</v>
       </c>
       <c r="N24" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O24" t="s">
-        <v>3627</v>
+        <v>3619</v>
       </c>
       <c r="P24" t="n">
         <v>77892</v>
@@ -21250,30 +20857,30 @@
         <v>1482</v>
       </c>
       <c r="E25" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F25" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G25" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>3628</v>
+        <v>3620</v>
       </c>
       <c r="K25" t="s">
-        <v>3629</v>
+        <v>3621</v>
       </c>
       <c r="L25" t="s">
-        <v>3628</v>
+        <v>3620</v>
       </c>
       <c r="M25" t="s">
-        <v>3630</v>
+        <v>3622</v>
       </c>
       <c r="N25" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O25"/>
       <c r="P25" t="n">
@@ -21294,33 +20901,33 @@
         <v>963</v>
       </c>
       <c r="E26" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F26" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G26" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>3631</v>
+        <v>3623</v>
       </c>
       <c r="K26" t="s">
-        <v>3632</v>
+        <v>3624</v>
       </c>
       <c r="L26" t="s">
-        <v>3631</v>
+        <v>3623</v>
       </c>
       <c r="M26" t="s">
-        <v>3633</v>
+        <v>3625</v>
       </c>
       <c r="N26" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O26" t="s">
-        <v>3634</v>
+        <v>3626</v>
       </c>
       <c r="P26" t="n">
         <v>81135</v>
@@ -21340,33 +20947,33 @@
         <v>1758</v>
       </c>
       <c r="E27" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F27" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G27" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>3525</v>
+        <v>3517</v>
       </c>
       <c r="K27" t="s">
-        <v>3635</v>
+        <v>3627</v>
       </c>
       <c r="L27" t="s">
-        <v>3525</v>
+        <v>3517</v>
       </c>
       <c r="M27" t="s">
-        <v>3636</v>
+        <v>3628</v>
       </c>
       <c r="N27" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O27" t="s">
-        <v>3527</v>
+        <v>3519</v>
       </c>
       <c r="P27" t="n">
         <v>82842</v>
@@ -21386,33 +20993,33 @@
         <v>993</v>
       </c>
       <c r="E28" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F28" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G28" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>3637</v>
+        <v>3629</v>
       </c>
       <c r="K28" t="s">
-        <v>3638</v>
+        <v>3630</v>
       </c>
       <c r="L28" t="s">
-        <v>3637</v>
+        <v>3629</v>
       </c>
       <c r="M28" t="s">
-        <v>3639</v>
+        <v>3631</v>
       </c>
       <c r="N28" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O28" t="s">
-        <v>3640</v>
+        <v>3632</v>
       </c>
       <c r="P28" t="n">
         <v>84564</v>
@@ -21432,30 +21039,30 @@
         <v>1884</v>
       </c>
       <c r="E29" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F29" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G29" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>3501</v>
+        <v>3493</v>
       </c>
       <c r="K29" t="s">
-        <v>3641</v>
+        <v>3633</v>
       </c>
       <c r="L29" t="s">
-        <v>3501</v>
+        <v>3493</v>
       </c>
       <c r="M29" t="s">
-        <v>3593</v>
+        <v>3585</v>
       </c>
       <c r="N29" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O29"/>
       <c r="P29" t="n">
@@ -21476,33 +21083,33 @@
         <v>2820</v>
       </c>
       <c r="E30" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F30" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G30" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>3530</v>
+        <v>3522</v>
       </c>
       <c r="K30" t="s">
-        <v>3642</v>
+        <v>3634</v>
       </c>
       <c r="L30" t="s">
-        <v>3530</v>
+        <v>3522</v>
       </c>
       <c r="M30" t="s">
-        <v>3643</v>
+        <v>3635</v>
       </c>
       <c r="N30" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O30" t="s">
-        <v>3532</v>
+        <v>3524</v>
       </c>
       <c r="P30" t="n">
         <v>96528</v>
@@ -21522,33 +21129,33 @@
         <v>453</v>
       </c>
       <c r="E31" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F31" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G31" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>3644</v>
+        <v>3636</v>
       </c>
       <c r="K31" t="s">
-        <v>3645</v>
+        <v>3637</v>
       </c>
       <c r="L31" t="s">
-        <v>3644</v>
+        <v>3636</v>
       </c>
       <c r="M31" t="s">
-        <v>3646</v>
+        <v>3638</v>
       </c>
       <c r="N31" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O31" t="s">
-        <v>3647</v>
+        <v>3639</v>
       </c>
       <c r="P31" t="n">
         <v>98569</v>
@@ -21568,30 +21175,30 @@
         <v>393</v>
       </c>
       <c r="E32" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F32" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G32" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>3648</v>
+        <v>3640</v>
       </c>
       <c r="K32" t="s">
-        <v>3649</v>
+        <v>3641</v>
       </c>
       <c r="L32" t="s">
-        <v>3648</v>
+        <v>3640</v>
       </c>
       <c r="M32" t="s">
-        <v>3593</v>
+        <v>3585</v>
       </c>
       <c r="N32" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O32"/>
       <c r="P32" t="n">
@@ -21612,33 +21219,33 @@
         <v>1185</v>
       </c>
       <c r="E33" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F33" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G33" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>3516</v>
+        <v>3508</v>
       </c>
       <c r="K33" t="s">
-        <v>3650</v>
+        <v>3642</v>
       </c>
       <c r="L33" t="s">
-        <v>3516</v>
+        <v>3508</v>
       </c>
       <c r="M33" t="s">
-        <v>3651</v>
+        <v>3643</v>
       </c>
       <c r="N33" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O33" t="s">
-        <v>3518</v>
+        <v>3510</v>
       </c>
       <c r="P33" t="n">
         <v>99811</v>
@@ -21658,33 +21265,33 @@
         <v>1236</v>
       </c>
       <c r="E34" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F34" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G34" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>3535</v>
+        <v>3527</v>
       </c>
       <c r="K34" t="s">
-        <v>3652</v>
+        <v>3644</v>
       </c>
       <c r="L34" t="s">
-        <v>3535</v>
+        <v>3527</v>
       </c>
       <c r="M34" t="s">
-        <v>3653</v>
+        <v>3645</v>
       </c>
       <c r="N34" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O34" t="s">
-        <v>3536</v>
+        <v>3528</v>
       </c>
       <c r="P34" t="n">
         <v>101266</v>
@@ -21704,33 +21311,33 @@
         <v>1359</v>
       </c>
       <c r="E35" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F35" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G35" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>3549</v>
+        <v>3541</v>
       </c>
       <c r="K35" t="s">
-        <v>3654</v>
+        <v>3646</v>
       </c>
       <c r="L35" t="s">
-        <v>3549</v>
+        <v>3541</v>
       </c>
       <c r="M35" t="s">
-        <v>3655</v>
+        <v>3647</v>
       </c>
       <c r="N35" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O35" t="s">
-        <v>3551</v>
+        <v>3543</v>
       </c>
       <c r="P35" t="n">
         <v>103291</v>
@@ -21750,33 +21357,33 @@
         <v>815</v>
       </c>
       <c r="E36" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F36" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G36" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>3502</v>
+        <v>3494</v>
       </c>
       <c r="K36" t="s">
-        <v>3656</v>
+        <v>3648</v>
       </c>
       <c r="L36" t="s">
-        <v>3502</v>
+        <v>3494</v>
       </c>
       <c r="M36" t="s">
-        <v>3657</v>
+        <v>3649</v>
       </c>
       <c r="N36" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O36" t="s">
-        <v>3503</v>
+        <v>3495</v>
       </c>
       <c r="P36" t="n">
         <v>104684</v>
@@ -21796,33 +21403,33 @@
         <v>1314</v>
       </c>
       <c r="E37" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F37" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G37" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>3658</v>
+        <v>3650</v>
       </c>
       <c r="K37" t="s">
-        <v>3659</v>
+        <v>3651</v>
       </c>
       <c r="L37" t="s">
-        <v>3658</v>
+        <v>3650</v>
       </c>
       <c r="M37" t="s">
-        <v>3660</v>
+        <v>3652</v>
       </c>
       <c r="N37" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O37" t="s">
-        <v>3661</v>
+        <v>3653</v>
       </c>
       <c r="P37" t="n">
         <v>106712</v>
@@ -21842,33 +21449,33 @@
         <v>297</v>
       </c>
       <c r="E38" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F38" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G38" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>3662</v>
+        <v>3654</v>
       </c>
       <c r="K38" t="s">
-        <v>3663</v>
+        <v>3655</v>
       </c>
       <c r="L38" t="s">
-        <v>3662</v>
+        <v>3654</v>
       </c>
       <c r="M38" t="s">
-        <v>3664</v>
+        <v>3656</v>
       </c>
       <c r="N38" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O38" t="s">
-        <v>3665</v>
+        <v>3657</v>
       </c>
       <c r="P38" t="n">
         <v>107974</v>
@@ -21888,33 +21495,33 @@
         <v>1074</v>
       </c>
       <c r="E39" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F39" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G39" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>3666</v>
+        <v>3658</v>
       </c>
       <c r="K39" t="s">
-        <v>3667</v>
+        <v>3659</v>
       </c>
       <c r="L39" t="s">
-        <v>3666</v>
+        <v>3658</v>
       </c>
       <c r="M39" t="s">
-        <v>3668</v>
+        <v>3660</v>
       </c>
       <c r="N39" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O39" t="s">
-        <v>3669</v>
+        <v>3661</v>
       </c>
       <c r="P39" t="n">
         <v>109348</v>
@@ -21934,33 +21541,33 @@
         <v>1290</v>
       </c>
       <c r="E40" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F40" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G40" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>3523</v>
+        <v>3515</v>
       </c>
       <c r="K40" t="s">
-        <v>3670</v>
+        <v>3662</v>
       </c>
       <c r="L40" t="s">
-        <v>3523</v>
+        <v>3515</v>
       </c>
       <c r="M40" t="s">
-        <v>3671</v>
+        <v>3663</v>
       </c>
       <c r="N40" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O40" t="s">
-        <v>3524</v>
+        <v>3516</v>
       </c>
       <c r="P40" t="n">
         <v>110672</v>
@@ -21980,33 +21587,33 @@
         <v>1341</v>
       </c>
       <c r="E41" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F41" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G41" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" t="s">
-        <v>3672</v>
+        <v>3664</v>
       </c>
       <c r="K41" t="s">
-        <v>3673</v>
+        <v>3665</v>
       </c>
       <c r="L41" t="s">
-        <v>3672</v>
+        <v>3664</v>
       </c>
       <c r="M41" t="s">
-        <v>3674</v>
+        <v>3666</v>
       </c>
       <c r="N41" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O41" t="s">
-        <v>3675</v>
+        <v>3667</v>
       </c>
       <c r="P41" t="n">
         <v>112424</v>
@@ -22026,33 +21633,33 @@
         <v>1419</v>
       </c>
       <c r="E42" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F42" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G42" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" t="s">
-        <v>3504</v>
+        <v>3496</v>
       </c>
       <c r="K42" t="s">
-        <v>3676</v>
+        <v>3668</v>
       </c>
       <c r="L42" t="s">
-        <v>3504</v>
+        <v>3496</v>
       </c>
       <c r="M42" t="s">
-        <v>3677</v>
+        <v>3669</v>
       </c>
       <c r="N42" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O42" t="s">
-        <v>3505</v>
+        <v>3497</v>
       </c>
       <c r="P42" t="n">
         <v>114208</v>
@@ -22072,33 +21679,33 @@
         <v>282</v>
       </c>
       <c r="E43" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F43" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G43" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" t="s">
-        <v>3509</v>
+        <v>3501</v>
       </c>
       <c r="K43" t="s">
-        <v>3678</v>
+        <v>3670</v>
       </c>
       <c r="L43" t="s">
-        <v>3509</v>
+        <v>3501</v>
       </c>
       <c r="M43" t="s">
-        <v>3679</v>
+        <v>3671</v>
       </c>
       <c r="N43" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O43" t="s">
-        <v>3511</v>
+        <v>3503</v>
       </c>
       <c r="P43" t="n">
         <v>115760</v>
@@ -22118,33 +21725,33 @@
         <v>1626</v>
       </c>
       <c r="E44" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F44" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G44" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44" t="s">
-        <v>3680</v>
+        <v>3672</v>
       </c>
       <c r="K44" t="s">
-        <v>3681</v>
+        <v>3673</v>
       </c>
       <c r="L44" t="s">
-        <v>3680</v>
+        <v>3672</v>
       </c>
       <c r="M44" t="s">
-        <v>3682</v>
+        <v>3674</v>
       </c>
       <c r="N44" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O44" t="s">
-        <v>3683</v>
+        <v>3675</v>
       </c>
       <c r="P44" t="n">
         <v>118626</v>
@@ -22164,33 +21771,33 @@
         <v>1593</v>
       </c>
       <c r="E45" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F45" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G45" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" t="s">
-        <v>3521</v>
+        <v>3513</v>
       </c>
       <c r="K45" t="s">
-        <v>3684</v>
+        <v>3676</v>
       </c>
       <c r="L45" t="s">
-        <v>3521</v>
+        <v>3513</v>
       </c>
       <c r="M45" t="s">
-        <v>3685</v>
+        <v>3677</v>
       </c>
       <c r="N45" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O45" t="s">
-        <v>3522</v>
+        <v>3514</v>
       </c>
       <c r="P45" t="n">
         <v>120887</v>
@@ -22210,30 +21817,30 @@
         <v>216</v>
       </c>
       <c r="E46" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F46" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G46" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" t="s">
-        <v>3686</v>
+        <v>3678</v>
       </c>
       <c r="K46" t="s">
-        <v>3687</v>
+        <v>3679</v>
       </c>
       <c r="L46" t="s">
-        <v>3686</v>
+        <v>3678</v>
       </c>
       <c r="M46" t="s">
-        <v>3593</v>
+        <v>3585</v>
       </c>
       <c r="N46" t="s">
-        <v>3584</v>
+        <v>3576</v>
       </c>
       <c r="O46"/>
       <c r="P46" t="n">
@@ -22254,33 +21861,33 @@
         <v>702</v>
       </c>
       <c r="E47" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F47" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G47" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47" t="s">
-        <v>3688</v>
+        <v>3680</v>
       </c>
       <c r="K47" t="s">
-        <v>3689</v>
+        <v>3681</v>
       </c>
       <c r="L47" t="s">
-        <v>3688</v>
+        <v>3680</v>
       </c>
       <c r="M47" t="s">
-        <v>3690</v>
+        <v>3682</v>
       </c>
       <c r="N47" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O47" t="s">
-        <v>3691</v>
+        <v>3683</v>
       </c>
       <c r="P47" t="n">
         <v>123240</v>
@@ -22300,33 +21907,33 @@
         <v>1572</v>
       </c>
       <c r="E48" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F48" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G48" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>3494</v>
+        <v>3486</v>
       </c>
       <c r="K48" t="s">
-        <v>3692</v>
+        <v>3684</v>
       </c>
       <c r="L48" t="s">
-        <v>3494</v>
+        <v>3486</v>
       </c>
       <c r="M48" t="s">
-        <v>3693</v>
+        <v>3685</v>
       </c>
       <c r="N48" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O48" t="s">
-        <v>3495</v>
+        <v>3487</v>
       </c>
       <c r="P48" t="n">
         <v>124894</v>
@@ -22346,33 +21953,33 @@
         <v>972</v>
       </c>
       <c r="E49" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F49" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G49" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H49"/>
       <c r="I49"/>
       <c r="J49" t="s">
-        <v>3694</v>
+        <v>3686</v>
       </c>
       <c r="K49" t="s">
-        <v>3695</v>
+        <v>3687</v>
       </c>
       <c r="L49" t="s">
-        <v>3694</v>
+        <v>3686</v>
       </c>
       <c r="M49" t="s">
-        <v>3696</v>
+        <v>3688</v>
       </c>
       <c r="N49" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O49" t="s">
-        <v>3697</v>
+        <v>3689</v>
       </c>
       <c r="P49" t="n">
         <v>127006</v>
@@ -22392,33 +21999,33 @@
         <v>1341</v>
       </c>
       <c r="E50" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F50" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G50" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H50"/>
       <c r="I50"/>
       <c r="J50" t="s">
-        <v>3698</v>
+        <v>3690</v>
       </c>
       <c r="K50" t="s">
-        <v>3699</v>
+        <v>3691</v>
       </c>
       <c r="L50" t="s">
-        <v>3698</v>
+        <v>3690</v>
       </c>
       <c r="M50" t="s">
-        <v>3700</v>
+        <v>3692</v>
       </c>
       <c r="N50" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O50" t="s">
-        <v>3701</v>
+        <v>3693</v>
       </c>
       <c r="P50" t="n">
         <v>128450</v>
@@ -22438,33 +22045,33 @@
         <v>968</v>
       </c>
       <c r="E51" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F51" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G51" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
       <c r="J51" t="s">
-        <v>3519</v>
+        <v>3511</v>
       </c>
       <c r="K51" t="s">
-        <v>3702</v>
+        <v>3694</v>
       </c>
       <c r="L51" t="s">
-        <v>3519</v>
+        <v>3511</v>
       </c>
       <c r="M51" t="s">
-        <v>3703</v>
+        <v>3695</v>
       </c>
       <c r="N51" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O51" t="s">
-        <v>3520</v>
+        <v>3512</v>
       </c>
       <c r="P51" t="n">
         <v>129964</v>
@@ -22484,33 +22091,33 @@
         <v>717</v>
       </c>
       <c r="E52" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F52" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G52" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H52"/>
       <c r="I52"/>
       <c r="J52" t="s">
-        <v>3704</v>
+        <v>3696</v>
       </c>
       <c r="K52" t="s">
-        <v>3705</v>
+        <v>3697</v>
       </c>
       <c r="L52" t="s">
-        <v>3704</v>
+        <v>3696</v>
       </c>
       <c r="M52" t="s">
-        <v>3706</v>
+        <v>3698</v>
       </c>
       <c r="N52" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O52" t="s">
-        <v>3707</v>
+        <v>3699</v>
       </c>
       <c r="P52" t="n">
         <v>131088</v>
@@ -22530,33 +22137,33 @@
         <v>876</v>
       </c>
       <c r="E53" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F53" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G53" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H53"/>
       <c r="I53"/>
       <c r="J53" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="K53" t="s">
-        <v>3709</v>
+        <v>3701</v>
       </c>
       <c r="L53" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="M53" t="s">
-        <v>3710</v>
+        <v>3702</v>
       </c>
       <c r="N53" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O53" t="s">
-        <v>3711</v>
+        <v>3703</v>
       </c>
       <c r="P53" t="n">
         <v>132484</v>
@@ -22576,33 +22183,33 @@
         <v>1980</v>
       </c>
       <c r="E54" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F54" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G54" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H54"/>
       <c r="I54"/>
       <c r="J54" t="s">
-        <v>3712</v>
+        <v>3704</v>
       </c>
       <c r="K54" t="s">
-        <v>3713</v>
+        <v>3705</v>
       </c>
       <c r="L54" t="s">
-        <v>3712</v>
+        <v>3704</v>
       </c>
       <c r="M54" t="s">
-        <v>3598</v>
+        <v>3590</v>
       </c>
       <c r="N54" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O54" t="s">
-        <v>3714</v>
+        <v>3706</v>
       </c>
       <c r="P54" t="n">
         <v>135544</v>
@@ -22622,33 +22229,33 @@
         <v>1575</v>
       </c>
       <c r="E55" t="s">
-        <v>3563</v>
+        <v>3555</v>
       </c>
       <c r="F55" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G55" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H55"/>
       <c r="I55"/>
       <c r="J55" t="s">
-        <v>3545</v>
+        <v>3537</v>
       </c>
       <c r="K55" t="s">
-        <v>3715</v>
+        <v>3707</v>
       </c>
       <c r="L55" t="s">
-        <v>3545</v>
+        <v>3537</v>
       </c>
       <c r="M55" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="N55" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O55" t="s">
-        <v>3546</v>
+        <v>3538</v>
       </c>
       <c r="P55" t="n">
         <v>137668</v>
@@ -22668,33 +22275,33 @@
         <v>1158</v>
       </c>
       <c r="E56" t="s">
-        <v>3576</v>
+        <v>3568</v>
       </c>
       <c r="F56" t="s">
-        <v>3564</v>
+        <v>3556</v>
       </c>
       <c r="G56" t="s">
-        <v>3562</v>
+        <v>3554</v>
       </c>
       <c r="H56"/>
       <c r="I56"/>
       <c r="J56" t="s">
-        <v>3543</v>
+        <v>3535</v>
       </c>
       <c r="K56" t="s">
-        <v>3717</v>
+        <v>3709</v>
       </c>
       <c r="L56" t="s">
-        <v>3543</v>
+        <v>3535</v>
       </c>
       <c r="M56" t="s">
-        <v>3718</v>
+        <v>3710</v>
       </c>
       <c r="N56" t="s">
-        <v>3568</v>
+        <v>3560</v>
       </c>
       <c r="O56" t="s">
-        <v>3544</v>
+        <v>3536</v>
       </c>
       <c r="P56" t="n">
         <v>139272</v>
